--- a/nyc_taxi_analysis/04_graphs/graph_index.xlsx
+++ b/nyc_taxi_analysis/04_graphs/graph_index.xlsx
@@ -431,14 +431,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="48" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="43" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="70" customWidth="1" min="7" max="7"/>
     <col width="70" customWidth="1" min="8" max="8"/>
@@ -501,17 +501,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>585c40398a_hexbin.png</t>
+          <t>cdf62daa38_density_trend.png</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>average_speed_mph_per_trip_distance</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -521,7 +521,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>(average_speed_mph / trip_distance)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -529,39 +529,39 @@
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against fare_amount Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against average_speed_mph_per_trip_distance Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of average_speed_mph_per_trip_distance, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.966 rho=+0.957 MI=0.423 stability=1.00 dir=positive (very strong)</t>
+          <t>n=3,509,466 r=-0.426 rho=-0.889 MI=0.251 stability=1.00 dir=negative (very strong)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ev_e130deeecc58496a</t>
+          <t>ev_2a3db3b226f3412a</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>f57010fa3f_hexbin.png</t>
+          <t>b74d39221e_density_trend.png</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>trip_distance_times_trip_duration_minutes</t>
+          <t>trip_distance</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>(trip_distance * trip_duration_minutes)</t>
+          <t>trip_distance</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -579,17 +579,17 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against trip_distance_times_trip_duration_minutes Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against trip_distance Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of trip_distance, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.741 rho=+0.895 MI=0.288 stability=0.99 dir=positive (very strong)</t>
+          <t>n=3,509,466 r=+0.867 rho=+0.847 MI=0.229 stability=1.00 dir=positive (very strong)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>ev_a1f01c44dcee44e1</t>
+          <t>ev_4820137175de4b4b</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -601,17 +601,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>8ff62c05a9_hexbin.png</t>
+          <t>6de2708a55_density_trend.png</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>trip_duration_minutes</t>
+          <t>log_trip_distance</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>trip_duration_minutes</t>
+          <t>log(trip_distance)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -629,17 +629,17 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against trip_duration_minutes Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against log_trip_distance Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of log_trip_distance, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.699 rho=+0.889 MI=0.250 stability=1.00 dir=positive (very strong)</t>
+          <t>n=3,509,466 r=+0.700 rho=+0.847 MI=0.229 stability=1.00 dir=positive (very strong)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ev_01da41bb6c804816</t>
+          <t>ev_b79d45d26895414e</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -651,17 +651,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>b74d39221e_hexbin.png</t>
+          <t>5d42bca8aa_density_trend.png</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>trip_distance</t>
+          <t>trip_distance_per_passenger_count</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -671,47 +671,47 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>trip_distance</t>
+          <t>(trip_distance / passenger_count)</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3509466</v>
+        <v>2501017</v>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against trip_distance Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against trip_distance_per_passenger_count Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of trip_distance_per_passenger_count, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.867 rho=+0.847 dir=positive (very strong)</t>
+          <t>n=2,501,017 r=+0.845 rho=+0.834 MI=0.218 stability=1.00 dir=positive (very strong)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ev_22740fa3572c4e6e</t>
+          <t>ev_d50daed6805b4473</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2fc81ea1a5_hexbin.png</t>
+          <t>f16adabba4_density_trend.png</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fare_amount / trip_distance</t>
+          <t>passenger_count_times_trip_distance</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -721,25 +721,25 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>(fare_amount / trip_distance)</t>
+          <t>(passenger_count * trip_distance)</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3509466</v>
+        <v>2515206</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against fare_amount / trip_distance Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against passenger_count_times_trip_distance Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of passenger_count_times_trip_distance, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.041 rho=-0.452 MI=0.068 dir=positive (moderate)</t>
+          <t>n=2,515,206 r=+0.781 rho=+0.835 MI=0.218 stability=1.00 dir=positive (very strong)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>ev_5547f96e7fa744bf</t>
+          <t>ev_428ee888e36c4b9f</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -751,17 +751,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6de2708a55_hexbin.png</t>
+          <t>4371399e65_density_trend.png</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>log_trip_distance</t>
+          <t>average_speed_mph_times_trip_distance</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>log(trip_distance)</t>
+          <t>(average_speed_mph * trip_distance)</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -779,39 +779,39 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against log_trip_distance Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against average_speed_mph_times_trip_distance Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of average_speed_mph_times_trip_distance, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.700 rho=+0.847 dir=positive (very strong)</t>
+          <t>n=3,509,466 r=+0.779 rho=+0.726 dir=positive (strong)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>ev_18f103a535b642e1</t>
+          <t>ev_0cf3a8a7ef4d4dde</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>mechanical</t>
+          <t>explained</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>880f84238d_hexbin.png</t>
+          <t>f1c1efba63_density_trend.png</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>trip_distance_per_trip_duration_minutes</t>
+          <t>fare_per_mile_times_trip_distance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>(trip_distance / trip_duration_minutes)</t>
+          <t>(fare_per_mile * trip_distance)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -829,17 +829,17 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against trip_distance_per_trip_duration_minutes Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against fare_per_mile_times_trip_distance Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of fare_per_mile_times_trip_distance, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.547 rho=+0.353 dir=positive (strong)</t>
+          <t>n=3,509,466 r=+0.966 rho=+0.957 MI=0.422 stability=1.00 dir=positive (very strong)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ev_3b75c4dc9d0f4b7a</t>
+          <t>ev_11e5c44dd4774171</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -851,17 +851,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>68230704e6_hexbin.png</t>
+          <t>f141556f75_density_trend.png</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>trip_duration_minutes_per_trip_distance</t>
+          <t>log1p_trip_distance</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>(trip_duration_minutes / trip_distance)</t>
+          <t>log1p(trip_distance)</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -879,49 +879,49 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against trip_duration_minutes_per_trip_distance Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against log1p_trip_distance Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of log1p_trip_distance, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.026 rho=-0.353 MI=0.049 dir=positive (moderate)</t>
+          <t>n=3,509,466 r=+0.804 rho=+0.847 MI=0.229 stability=1.00 dir=positive (very strong)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>ev_03280601ea95405c</t>
+          <t>ev_946845877d1c47b9</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>mechanical</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>grp:paymen_box.png</t>
+          <t>f3e14fa57f_density_trend.png</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>box</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>payment_type</t>
+          <t>fare_per_mile_per_trip_distance</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>fare_amount</t>
+          <t>total_amount</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>payment_type groups</t>
+          <t>(fare_per_mile / trip_distance)</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -929,17 +929,17 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>A box of fare_amount against payment_type Rendering strategy: all rows summarised per category (median, IQR, 1.5-IQR whiskers). Each box summarises the distribution within one category level (median, interquartile range, whiskers at 1.5 IQR).</t>
+          <t>A density trend of total_amount against fare_per_mile_per_trip_distance Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of fare_per_mile_per_trip_distance, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 eta=0.152 dir=undetermined (weak)</t>
+          <t>n=3,509,466 r=+0.041 rho=-0.737 MI=0.159 stability=0.97 dir=positive (strong)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>ev_8dd1e8fe121a4599</t>
+          <t>ev_8f3f87e007964eba</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -951,17 +951,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>f141556f75_hexbin.png</t>
+          <t>118c265b17_density_trend.png</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>log1p_trip_distance</t>
+          <t>fare_per_mile</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>log1p(trip_distance)</t>
+          <t>fare_per_mile</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -979,17 +979,17 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against log1p_trip_distance Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against fare_per_mile Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of fare_per_mile, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.804 rho=+0.847 MI=0.229 stability=1.00 dir=positive (very strong)</t>
+          <t>n=3,509,466 r=+0.041 rho=-0.452 MI=0.068 dir=positive (moderate)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ev_030121cde85e4d91</t>
+          <t>ev_f69fdc515b1d4f7a</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1001,17 +1001,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5d42bca8aa_hexbin.png</t>
+          <t>8ff62c05a9_density_trend.png</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>trip_distance_per_passenger_count</t>
+          <t>trip_duration_minutes</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1021,25 +1021,25 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>(trip_distance / passenger_count)</t>
+          <t>trip_duration_minutes</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2501017</v>
+        <v>3509466</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against trip_distance_per_passenger_count Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against trip_duration_minutes Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of trip_duration_minutes, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>n=2,501,017 r=+0.845 rho=+0.834 MI=0.218 stability=1.00 dir=positive (very strong)</t>
+          <t>n=3,509,466 r=+0.699 rho=+0.889 MI=0.250 stability=1.00 dir=positive (very strong)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ev_73df613937424df8</t>
+          <t>ev_b1c7a87c598f49d7</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1051,17 +1051,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>f16adabba4_hexbin.png</t>
+          <t>edbd559ad6_density_trend.png</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>density_trend</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>passenger_count_times_trip_distance</t>
+          <t>trip_duration_minutes_per_tip_fraction_of_fare</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1071,47 +1071,47 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>(passenger_count * trip_distance)</t>
+          <t>(trip_duration_minutes / tip_fraction_of_fare)</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>2515206</v>
+        <v>2065405</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against passenger_count_times_trip_distance Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A density trend of total_amount against trip_duration_minutes_per_tip_fraction_of_fare Rendering strategy: all rows aggregated into a density background, with the conditional mean of y within quantile bins of x overlaid as a curve with 95% confidence bands. The shaded background is a density map: colour is how many records fall in each cell (log scale), NOT the value of a third variable. The bold line is the CONDITIONAL MEAN of total_amount within 40 quantile bins of trip_duration_minutes_per_tip_fraction_of_fare, with a 95% confidence band. Read the bold line for the shape of the relationship; read the background for where the data actually is.</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>n=2,515,206 r=+0.781 rho=+0.835 MI=0.218 stability=1.00 dir=positive (very strong)</t>
+          <t>n=2,065,405 r=+0.047 rho=+0.810 MI=0.196 stability=0.87 dir=positive (very strong)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ev_4d5e655d4d3d4d74</t>
+          <t>ev_a0e6bb1d2bd94e2c</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>explained</t>
+          <t>mechanical</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>db5734034b_hexbin.png</t>
+          <t>grp_is_air_box.png</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>box</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>passenger_count_per_trip_distance</t>
+          <t>is_airport_pickup</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(passenger_count / trip_distance)</t>
+          <t>is_airport_pickup groups</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -1129,39 +1129,39 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against passenger_count_per_trip_distance Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A box of total_amount against is_airport_pickup Rendering strategy: all rows summarised per category (median, IQR, 1.5-IQR whiskers). Each box summarises the distribution within one category level (median, interquartile range, whiskers at 1.5 IQR).</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>n=2,515,206 r=-0.159 rho=-0.821 MI=0.214 stability=0.94 dir=negative (very strong)</t>
+          <t>n=2,515,206 eta=0.643 dir=undetermined (strong)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ev_24a0da8d14304bf0</t>
+          <t>ev_b1355be178d74319</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>unresolved</t>
+          <t>mechanical</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ef027e69ae_hexbin.png</t>
+          <t>grp_Rateco_box.png</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hexbin</t>
+          <t>box</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>log_trip_duration_minutes</t>
+          <t>RatecodeID</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1171,78 +1171,28 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>log(trip_duration_minutes)</t>
+          <t>RatecodeID groups</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3509466</v>
+        <v>2515206</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>A hexbin of total_amount against log_trip_duration_minutes Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
+          <t>A box of total_amount against RatecodeID Rendering strategy: all rows summarised per category (median, IQR, 1.5-IQR whiskers). Each box summarises the distribution within one category level (median, interquartile range, whiskers at 1.5 IQR).</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>n=3,509,466 r=+0.685 rho=+0.889 MI=0.250 stability=1.00 dir=positive (very strong)</t>
+          <t>n=2,515,206 eta=0.679 dir=undetermined (strong)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>ev_5f943dfd00eb4476</t>
+          <t>ev_7732a65757b5434f</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
-        <is>
-          <t>explained</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>160a090832_hexbin.png</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>hexbin</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>passenger_count_times_trip_duration_minutes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>total_amount</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>(passenger_count * trip_duration_minutes)</t>
-        </is>
-      </c>
-      <c r="F16" t="n">
-        <v>2515206</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>A hexbin of total_amount against passenger_count_times_trip_duration_minutes Rendering strategy: all rows aggregated into hexagonal density cells (log colour scale). Colour encodes how many records fall in each hexagonal cell (log scale), not the value of a third variable. The line is an ordinary least-squares fit.</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr">
-        <is>
-          <t>n=2,515,206 r=+0.634 rho=+0.839 MI=0.218 stability=1.00 dir=positive (very strong)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>ev_991c30c994024b1d</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
         <is>
           <t>explained</t>
         </is>
